--- a/sheet/PassiveCardData.xlsx
+++ b/sheet/PassiveCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BE2BF7-158F-4A89-9F6D-BC6870A6FD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BC1963-7EBC-4165-9C62-3406F4FD03FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5940" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,14 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>最大生命值加2。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>附肢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>手牌基数加1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>临阵陷阱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>支援控制</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,14 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以支付3MP，制造1张点数为2的化身牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以支付5MP，制造1张点数为3的化身牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>分身</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -164,6 +144,34 @@
   </si>
   <si>
     <t>effect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以支付2MP，制造1张点数为2的化身牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以支付3MP，制造1张点数为3的化身牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大HP加2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大MP加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三只手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵活陷阱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -492,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -503,7 +511,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -520,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -532,19 +540,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -556,141 +564,153 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="114" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="114" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="114" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="1"/>
+      <c r="D17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sheet/PassiveCardData.xlsx
+++ b/sheet/PassiveCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BC1963-7EBC-4165-9C62-3406F4FD03FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AE017C-7DDE-4A57-AA06-269EAD43A212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="3480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,14 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>变速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以按任意顺序结算场上所有由玩家控制的牌的回合结束时效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>分身</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -172,6 +164,14 @@
   </si>
   <si>
     <t>灵活陷阱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速支援</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家控制的牌发动呼唤效果时，可以将被呼唤的牌放在后置位。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -511,7 +511,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -540,19 +540,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -564,25 +564,25 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="8" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -636,79 +636,79 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="114" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:5" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" ht="114" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1"/>
     </row>

--- a/sheet/PassiveCardData.xlsx
+++ b/sheet/PassiveCardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AE017C-7DDE-4A57-AA06-269EAD43A212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8EE3F7-0732-4EF2-99D5-E42C8C166DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="3480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6435" yWindow="4080" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以将陷阱牌打出到敌对侧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>支援控制</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以将化身牌出在敌对侧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>计划</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -95,46 +87,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以用技能牌替换场上的技能牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>多重施法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>预知梦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重整时限1次：可以重抽场上和手牌中任意张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急补员</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用目标为场上的1张牌的法术时：可以额外消耗1MP，然后额外指定1个目标。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>失去最后1张手牌时：可以从主牌堆抽1张牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>翻选时：可以将未被选择的牌按任意顺序放回原牌堆顶。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>支配</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交锋获胜时：可以支付1MP，将敌对侧1张怪物牌加入手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>effect</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -172,6 +132,62 @@
   </si>
   <si>
     <t>玩家控制的牌发动呼唤效果时，可以将被呼唤的牌放在后置位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将化身牌出在任意阵营。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将陷阱牌打出到任意阵营。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻选时，可以将未被选择的牌按任意顺序放回原牌堆顶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用目标为场上的1张牌的法术时，可以额外消耗1MP，然后额外指定1个目标。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋获胜时，可以支付1MP，使1张地城阵营的怪物牌免死，然后将其加入手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以在回合开始阶段开始时打出手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以随时弃置1张道具牌并获得1金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重整旗鼓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具牌被弃置时，获得1金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重整后，可以重抽场上任意张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以用技能牌或化身牌替换场上的技能牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -500,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -511,7 +527,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -528,7 +544,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -540,19 +556,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -564,25 +580,25 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -594,123 +610,145 @@
     </row>
     <row r="8" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:5" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="114" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sheet/PassiveCardData.xlsx
+++ b/sheet/PassiveCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8EE3F7-0732-4EF2-99D5-E42C8C166DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C309E565-E03F-4913-9F94-43466669AD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="4080" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,10 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>最大MP加1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>第三只手</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,6 +184,18 @@
   </si>
   <si>
     <t>可以用技能牌或化身牌替换场上的技能牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大MP加2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>背包区容量加1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -592,133 +600,133 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>16</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -728,26 +736,38 @@
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="57" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/PassiveCardData.xlsx
+++ b/sheet/PassiveCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C309E565-E03F-4913-9F94-43466669AD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2977C763-467E-4308-8882-D2632FC80C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以将响应呼唤效果的牌放在发动呼唤效果的牌的后置位。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>伪装</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多重施法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>支配</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,14 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以支付2MP，制造1张点数为2的化身牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以支付3MP，制造1张点数为3的化身牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>意志</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,34 +107,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>快速支援</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家控制的牌发动呼唤效果时，可以将被呼唤的牌放在后置位。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以将化身牌出在任意阵营。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以将陷阱牌打出到任意阵营。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>快速部署</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>翻选时，可以将未被选择的牌按任意顺序放回原牌堆顶。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用目标为场上的1张牌的法术时，可以额外消耗1MP，然后额外指定1个目标。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交锋获胜时，可以支付1MP，使1张地城阵营的怪物牌免死，然后将其加入手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -167,10 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重整旗鼓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>精算</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -179,10 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重整后，可以重抽场上任意张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可以用技能牌或化身牌替换场上的技能牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -196,6 +148,46 @@
   </si>
   <si>
     <t>背包区容量加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以支付合计2点MP或HP，制造1张点数为2的化身牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以支付合计3点MP或HP，制造1张点数为3的化身牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>记忆力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法术表和技能池容量加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将陷阱牌打出到任意侧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将被召集牌放在召集牌的后置位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以将化身牌出在任意侧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻选时，可以不将未被选择的牌洗回原牌堆，而是按任意顺序放回原牌堆顶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新开门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>楼层重置后，可以立即重抽楼层区（包括奖励区）任意张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -524,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -535,7 +527,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -544,7 +536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -552,11 +544,11 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -564,19 +556,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -588,186 +580,174 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="57" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="57" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="57" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
